--- a/input/timetable/Спорт.xlsx
+++ b/input/timetable/Спорт.xlsx
@@ -280,12 +280,6 @@
     <t>Иностранный язык в проф. сфере, п/г2, К408</t>
   </si>
   <si>
-    <t>Психология инклюзивного общества (пр), ЭОиДОТ//</t>
-  </si>
-  <si>
-    <t>Физиология человека (пр), А433// Биохимия мышечной деятельности (пр),  А439</t>
-  </si>
-  <si>
     <t>Иностранный язык, п/г 1, Г104</t>
   </si>
   <si>
@@ -296,6 +290,12 @@
   </si>
   <si>
     <t>Учебная практика, ознакомительная практика, К210а//</t>
+  </si>
+  <si>
+    <t>// Психология инклюзивного общества (пр), К412</t>
+  </si>
+  <si>
+    <t>Физиология человека (пр), А431// Биохимия мышечной деятельности (пр),  А439</t>
   </si>
 </sst>
 </file>
@@ -1514,13 +1514,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2209,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="130" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D25" s="131"/>
       <c r="E25" s="131"/>
@@ -2257,11 +2257,11 @@
         <v>1</v>
       </c>
       <c r="C29" s="94" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D29" s="95"/>
       <c r="E29" s="95" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F29" s="96"/>
     </row>
@@ -2335,7 +2335,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="97" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D36" s="98"/>
       <c r="E36" s="98"/>
@@ -2631,7 +2631,7 @@
         <v>4</v>
       </c>
       <c r="C13" s="124" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" s="125"/>
       <c r="E13" s="125"/>
@@ -3184,9 +3184,7 @@
       <c r="B13" s="26">
         <v>5</v>
       </c>
-      <c r="C13" s="204" t="s">
-        <v>85</v>
-      </c>
+      <c r="C13" s="204"/>
       <c r="D13" s="205"/>
       <c r="E13" s="205"/>
       <c r="F13" s="206"/>
@@ -3340,7 +3338,9 @@
       <c r="B26" s="26">
         <v>5</v>
       </c>
-      <c r="C26" s="193"/>
+      <c r="C26" s="193" t="s">
+        <v>89</v>
+      </c>
       <c r="D26" s="194"/>
       <c r="E26" s="194"/>
       <c r="F26" s="195"/>

--- a/input/timetable/Спорт.xlsx
+++ b/input/timetable/Спорт.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28875" windowHeight="13155" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28875" windowHeight="13155"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="125">
   <si>
     <t>пара</t>
   </si>
@@ -70,6 +70,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -112,18 +115,33 @@
     <t>Лыжный спорт с методикой преподавания, л/б</t>
   </si>
   <si>
+    <t>Аустер Л.В., Родионова М.А.</t>
+  </si>
+  <si>
     <t>Гимнастика с методикой преподавания, Зал гимн.</t>
   </si>
   <si>
+    <t>Булгакова О.В., Савиных Л.Е.</t>
+  </si>
+  <si>
     <t>Спортивно-педагогические дисциплины, Зал гимн</t>
   </si>
   <si>
+    <t>Шнейдер В.Ю.</t>
+  </si>
+  <si>
     <t>214-31</t>
   </si>
   <si>
     <t>49.03.04 Спорт</t>
   </si>
   <si>
+    <t>Белоус П.В.</t>
+  </si>
+  <si>
+    <t>Савиных Л.Е., Булгакова О.В</t>
+  </si>
+  <si>
     <t>Плавание с методикой преподавания, бассейн (с 12.30)</t>
   </si>
   <si>
@@ -139,9 +157,18 @@
     <t>История России (лекция 32 ч)</t>
   </si>
   <si>
+    <t>Говорухина А.А.</t>
+  </si>
+  <si>
+    <t>Снигирев А.С., Жулепов В.И.</t>
+  </si>
+  <si>
     <t>Легкая атлетика с методикой преподавания, ЦАС</t>
   </si>
   <si>
+    <t>Снигирев А.С., Обухов С.М.</t>
+  </si>
+  <si>
     <t>Цифровая грамотность (лек 16 ч)</t>
   </si>
   <si>
@@ -151,18 +178,33 @@
     <t>Основы проектной деятельности (лек 16 ч)</t>
   </si>
   <si>
+    <t>Алькова С.Ю.</t>
+  </si>
+  <si>
     <t>Философия (лек 32 ч)</t>
   </si>
   <si>
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Замятина М.С.</t>
+  </si>
+  <si>
     <t>Спортивно-педагогические дисциплины,  Зал 2</t>
   </si>
   <si>
+    <t>Лосев А.В.</t>
+  </si>
+  <si>
     <t>Легкая атлетика с методикой преподавания,  ЦАС</t>
   </si>
   <si>
+    <t>Лосев В.Ю.</t>
+  </si>
+  <si>
+    <t>Родионов В.А.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (пр), К209</t>
   </si>
   <si>
@@ -202,45 +244,96 @@
     <t>Теория и методика спортивной тренировки        (ТО: 02.02.2026-06.06.2026)</t>
   </si>
   <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
+    <t>Вариясова Е.В.</t>
+  </si>
+  <si>
+    <t>Подлуцкая К.А.; Джумаева А.А.</t>
+  </si>
+  <si>
+    <t>Литовченко О.Г.</t>
+  </si>
+  <si>
+    <t>Ветрова Д.Н.</t>
+  </si>
+  <si>
     <t>// Спортивно-педагогические дисциплины, ЦАС</t>
   </si>
   <si>
     <t>Психология физической культуры (лек), К202//</t>
   </si>
   <si>
+    <t xml:space="preserve"> Обухов С.М., Снигирев А.С.</t>
+  </si>
+  <si>
+    <t>Гаврилова Н.В.</t>
+  </si>
+  <si>
+    <t>Джумаева А.А.; Воробьева А.Д.</t>
+  </si>
+  <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
     <t>Спортивно-педагогические дисциплины,  ЦАС</t>
   </si>
   <si>
     <t>Иностранный язык в проф. сфере, п/г1, К412</t>
   </si>
   <si>
+    <t>Кочиева Д.И.</t>
+  </si>
+  <si>
     <t>Психология инклюзивного общества (лек 16 ч)</t>
   </si>
   <si>
+    <t>Усаева Н.Р.</t>
+  </si>
+  <si>
+    <t>Мальков М.Н.</t>
+  </si>
+  <si>
     <t>Комплексный контроль в физической культуре и спорте (пр), К210</t>
   </si>
   <si>
+    <t>Воронюк Т.В.</t>
+  </si>
+  <si>
     <t>Теория спорта (лек), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Григорьев В.А.</t>
+  </si>
+  <si>
     <t>Теория спорта (пр), ЭОиДОТ</t>
   </si>
   <si>
     <t>Менеджмент физической культуры и спорта (лек), К425</t>
   </si>
   <si>
+    <t>Родионова М.А.</t>
+  </si>
+  <si>
     <t>Менеджмент физической культуры и спорта (пр), К425</t>
   </si>
   <si>
     <t>Спортивная социология (лек), К209</t>
   </si>
   <si>
+    <t>Савиных Л.Е.</t>
+  </si>
+  <si>
     <t>Спортивная социология (пр), К209</t>
   </si>
   <si>
     <t xml:space="preserve">ДВ 02.01: Футбол, зал 2; ДВ 02.02: Аэробика, сп/з </t>
   </si>
   <si>
+    <t>Ветошников А.Ю.; Булгакова О.В.</t>
+  </si>
+  <si>
     <t>Теория и методика физической культуры (лек), К202</t>
   </si>
   <si>
@@ -256,6 +349,9 @@
     <t>Русский язык и культура речи (пр), А514</t>
   </si>
   <si>
+    <t>Калинина Е.А./ Замятина М.С.</t>
+  </si>
+  <si>
     <t>Философия (пр), К427// Работа в команде (пр), К426</t>
   </si>
   <si>
@@ -280,6 +376,9 @@
     <t>Иностранный язык в проф. сфере, п/г2, К408</t>
   </si>
   <si>
+    <t>Барсегян С.Т./Говорухина А.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 1, Г104</t>
   </si>
   <si>
@@ -290,6 +389,9 @@
   </si>
   <si>
     <t>Учебная практика, ознакомительная практика, К210а//</t>
+  </si>
+  <si>
+    <t>Батыршина К.Г.</t>
   </si>
   <si>
     <t>// Психология инклюзивного общества (пр), К412</t>
@@ -404,7 +506,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -423,12 +525,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -558,6 +666,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -963,6 +1084,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -989,6 +1121,15 @@
         <color indexed="64"/>
       </left>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1078,7 +1219,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1112,28 +1253,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1160,10 +1304,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1172,13 +1316,14 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1189,195 +1334,302 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1385,197 +1637,125 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1906,18 +2086,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20" style="2" customWidth="1"/>
     <col min="4" max="5" width="18.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="6" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1925,15 +2105,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1941,39 +2121,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="43" t="s">
-        <v>16</v>
+      <c r="C6" s="45" t="s">
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -1983,35 +2163,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="152" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="152"/>
+      <c r="E7" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="47" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="C8" s="159" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="159"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>0</v>
@@ -2022,370 +2202,446 @@
       <c r="D9" s="18"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="G9" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="66"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24">
+      <c r="C10" s="160" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="161"/>
+      <c r="E10" s="161"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="69" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="103" t="s">
+      <c r="C11" s="86" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="72" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
+        <v>3</v>
+      </c>
+      <c r="C12" s="89" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="71" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
+        <v>4</v>
+      </c>
+      <c r="C13" s="92" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="94"/>
+      <c r="G13" s="66" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
+        <v>5</v>
+      </c>
+      <c r="C14" s="156"/>
+      <c r="D14" s="157"/>
+      <c r="E14" s="157"/>
+      <c r="F14" s="158"/>
+      <c r="G14" s="50"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="29">
+        <v>1</v>
+      </c>
+      <c r="C15" s="153" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="155"/>
+      <c r="G15" s="70" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
+        <v>2</v>
+      </c>
+      <c r="C16" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
+        <v>3</v>
+      </c>
+      <c r="C17" s="98"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="49"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
+        <v>4</v>
+      </c>
+      <c r="C18" s="101" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="102"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="71" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="30"/>
+      <c r="B19" s="27">
+        <v>7</v>
+      </c>
+      <c r="C19" s="104"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="106"/>
+      <c r="G19" s="49"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="29">
+        <v>1</v>
+      </c>
+      <c r="C20" s="107" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="108"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="109"/>
+      <c r="G20" s="69" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
+        <v>2</v>
+      </c>
+      <c r="C21" s="110" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="111"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="71" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25">
+        <v>3</v>
+      </c>
+      <c r="C22" s="119"/>
+      <c r="D22" s="120"/>
+      <c r="E22" s="120"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="60"/>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="30"/>
+      <c r="B23" s="27">
+        <v>4</v>
+      </c>
+      <c r="C23" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="96"/>
+      <c r="E23" s="96"/>
+      <c r="F23" s="97"/>
+      <c r="G23" s="73" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="23">
+        <v>1</v>
+      </c>
+      <c r="C24" s="113" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="114"/>
+      <c r="E24" s="114"/>
+      <c r="F24" s="115"/>
+      <c r="G24" s="64" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="24"/>
+      <c r="B25" s="23">
+        <v>2</v>
+      </c>
+      <c r="C25" s="116" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="117"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="118"/>
+      <c r="G25" s="68" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25">
+        <v>3</v>
+      </c>
+      <c r="C26" s="80" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="105"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+    </row>
+    <row r="27" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="24"/>
+      <c r="B27" s="25">
+        <v>4</v>
+      </c>
+      <c r="C27" s="92" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="65" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="30"/>
+      <c r="B28" s="27">
+        <v>5</v>
+      </c>
+      <c r="C28" s="125"/>
+      <c r="D28" s="126"/>
+      <c r="E28" s="126"/>
+      <c r="F28" s="127"/>
+      <c r="G28" s="59"/>
+    </row>
+    <row r="29" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="29">
+        <v>1</v>
+      </c>
+      <c r="C29" s="146" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="147"/>
+      <c r="E29" s="147" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" s="148"/>
+      <c r="G29" s="70" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="31"/>
+      <c r="B30" s="23">
+        <v>2</v>
+      </c>
+      <c r="C30" s="83"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="84"/>
+      <c r="F30" s="85"/>
+      <c r="G30" s="66"/>
+    </row>
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="31"/>
+      <c r="B31" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="106" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="107"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="108"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24">
+      <c r="C31" s="92"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="66"/>
+    </row>
+    <row r="32" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="34"/>
+      <c r="B32" s="27">
         <v>4</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C32" s="143" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="144"/>
+      <c r="E32" s="144"/>
+      <c r="F32" s="145"/>
+      <c r="G32" s="67" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="29">
+        <v>1</v>
+      </c>
+      <c r="C33" s="128"/>
+      <c r="D33" s="129"/>
+      <c r="E33" s="129"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="74"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="36"/>
+      <c r="B34" s="25">
+        <v>2</v>
+      </c>
+      <c r="C34" s="137" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="138"/>
+      <c r="E34" s="138"/>
+      <c r="F34" s="139"/>
+      <c r="G34" s="66" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="36"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="140"/>
+      <c r="D35" s="141"/>
+      <c r="E35" s="141"/>
+      <c r="F35" s="142"/>
+      <c r="G35" s="64"/>
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="37"/>
+      <c r="B36" s="27">
+        <v>5</v>
+      </c>
+      <c r="C36" s="149" t="s">
+        <v>120</v>
+      </c>
+      <c r="D36" s="150"/>
+      <c r="E36" s="150"/>
+      <c r="F36" s="151"/>
+      <c r="G36" s="67" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="38"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="131"/>
+      <c r="D37" s="132"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="133"/>
+      <c r="G37" s="40"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="41"/>
+      <c r="B38" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="134" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="135"/>
+      <c r="E38" s="135"/>
+      <c r="F38" s="136"/>
+      <c r="G38" s="69" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="42"/>
+      <c r="B39" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="59"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
-        <v>5</v>
-      </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="62"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="28">
-        <v>1</v>
-      </c>
-      <c r="C15" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="56"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
-        <v>2</v>
-      </c>
-      <c r="C16" s="106" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="107"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="108"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
-        <v>3</v>
-      </c>
-      <c r="C17" s="112"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="114"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24">
-        <v>4</v>
-      </c>
-      <c r="C18" s="115" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="117"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="29"/>
-      <c r="B19" s="26">
-        <v>7</v>
-      </c>
-      <c r="C19" s="118"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="120"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="28">
-        <v>1</v>
-      </c>
-      <c r="C20" s="121" t="s">
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="123"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
-        <v>2</v>
-      </c>
-      <c r="C21" s="124" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="125"/>
-      <c r="E21" s="125"/>
-      <c r="F21" s="126"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24">
-        <v>3</v>
-      </c>
-      <c r="C22" s="133"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="135"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="29"/>
-      <c r="B23" s="26">
-        <v>4</v>
-      </c>
-      <c r="C23" s="109" t="s">
-        <v>38</v>
-      </c>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="111"/>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="22">
-        <v>1</v>
-      </c>
-      <c r="C24" s="127" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="129"/>
-    </row>
-    <row r="25" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="22">
-        <v>2</v>
-      </c>
-      <c r="C25" s="130" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="131"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="132"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24">
-        <v>3</v>
-      </c>
-      <c r="C26" s="85" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="87"/>
-    </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="23"/>
-      <c r="B27" s="24">
-        <v>4</v>
-      </c>
-      <c r="C27" s="57" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59"/>
-    </row>
-    <row r="28" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="29"/>
-      <c r="B28" s="26">
-        <v>5</v>
-      </c>
-      <c r="C28" s="70"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="71"/>
-      <c r="F28" s="72"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="28">
-        <v>1</v>
-      </c>
-      <c r="C29" s="94" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" s="95"/>
-      <c r="E29" s="95" t="s">
-        <v>86</v>
-      </c>
-      <c r="F29" s="96"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="30"/>
-      <c r="B30" s="22">
-        <v>2</v>
-      </c>
-      <c r="C30" s="100"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="102"/>
-    </row>
-    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="30"/>
-      <c r="B31" s="24">
-        <v>3</v>
-      </c>
-      <c r="C31" s="57"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="59"/>
-    </row>
-    <row r="32" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="33"/>
-      <c r="B32" s="26">
-        <v>4</v>
-      </c>
-      <c r="C32" s="91" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="93"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="28">
-        <v>1</v>
-      </c>
-      <c r="C33" s="73"/>
-      <c r="D33" s="74"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="75"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="35"/>
-      <c r="B34" s="24">
-        <v>2</v>
-      </c>
-      <c r="C34" s="82" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="84"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="35"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="88"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="90"/>
-    </row>
-    <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="36"/>
-      <c r="B36" s="26">
-        <v>5</v>
-      </c>
-      <c r="C36" s="97" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="99"/>
-    </row>
-    <row r="37" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="78"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="39"/>
-      <c r="B38" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="79" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="81"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A39" s="40"/>
-      <c r="B39" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="85" t="s">
+    </row>
+    <row r="40" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="44"/>
+      <c r="B40" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D39" s="86"/>
-      <c r="E39" s="86"/>
-      <c r="F39" s="87"/>
-    </row>
-    <row r="40" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="42"/>
-      <c r="B40" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C40" s="67" t="s">
+      <c r="C40" s="122" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="123"/>
+      <c r="E40" s="123"/>
+      <c r="F40" s="124"/>
+      <c r="G40" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="69"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
         <v>13</v>
       </c>
@@ -2393,16 +2649,35 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C36:F36"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C11:F11"/>
@@ -2418,25 +2693,6 @@
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C40:F40"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C10:F10"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
@@ -2467,7 +2723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2476,12 +2732,13 @@
     <col min="4" max="4" width="20" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" style="2" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="2"/>
-    <col min="10" max="10" width="7.85546875" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="10" width="9.140625" style="2"/>
+    <col min="11" max="11" width="7.85546875" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2489,15 +2746,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2505,39 +2762,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="43" t="s">
-        <v>16</v>
+      <c r="C6" s="45" t="s">
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2547,35 +2804,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="45" t="s">
+      <c r="D7" s="152"/>
+      <c r="E7" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="47" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="C8" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="159"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>0</v>
@@ -2586,362 +2843,428 @@
       <c r="D9" s="18"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="G9" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="66"/>
-    </row>
-    <row r="11" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24">
+      <c r="C10" s="160"/>
+      <c r="D10" s="161"/>
+      <c r="E10" s="161"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="74"/>
+    </row>
+    <row r="11" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="145" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146" t="s">
-        <v>79</v>
-      </c>
-      <c r="F11" s="147"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="C11" s="184" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185" t="s">
+        <v>111</v>
+      </c>
+      <c r="F11" s="186"/>
+      <c r="G11" s="75" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="124" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="126"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24">
+      <c r="C12" s="110" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25">
         <v>4</v>
       </c>
-      <c r="C13" s="124" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="125"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="126"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
+      <c r="C13" s="110" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
         <v>5</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="62"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="28">
+      <c r="C14" s="156"/>
+      <c r="D14" s="157"/>
+      <c r="E14" s="157"/>
+      <c r="F14" s="158"/>
+      <c r="G14" s="58"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="29">
         <v>1</v>
       </c>
-      <c r="C15" s="54" t="s">
+      <c r="C15" s="153" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="155"/>
+      <c r="G15" s="74" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
+        <v>2</v>
+      </c>
+      <c r="C16" s="181" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="182"/>
+      <c r="E16" s="182"/>
+      <c r="F16" s="183"/>
+      <c r="G16" s="71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
+        <v>3</v>
+      </c>
+      <c r="C17" s="110"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="112"/>
+      <c r="G17" s="71"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25">
+        <v>4</v>
+      </c>
+      <c r="C18" s="104"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="49"/>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="57"/>
+      <c r="B19" s="33">
+        <v>5</v>
+      </c>
+      <c r="C19" s="110" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="111"/>
+      <c r="E19" s="111"/>
+      <c r="F19" s="112"/>
+      <c r="G19" s="66" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="29">
+        <v>1</v>
+      </c>
+      <c r="C20" s="134" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" s="135"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="136"/>
+      <c r="G20" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="56"/>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
         <v>2</v>
       </c>
-      <c r="C16" s="166" t="s">
+      <c r="C21" s="119"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="120"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="59"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25">
+        <v>3</v>
+      </c>
+      <c r="C22" s="193"/>
+      <c r="D22" s="194"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="195"/>
+      <c r="G22" s="61"/>
+    </row>
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="30"/>
+      <c r="B23" s="27">
+        <v>4</v>
+      </c>
+      <c r="C23" s="187"/>
+      <c r="D23" s="188"/>
+      <c r="E23" s="188"/>
+      <c r="F23" s="189"/>
+      <c r="G23" s="58"/>
+    </row>
+    <row r="24" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="23">
+        <v>2</v>
+      </c>
+      <c r="C24" s="140"/>
+      <c r="D24" s="141"/>
+      <c r="E24" s="141"/>
+      <c r="F24" s="142"/>
+      <c r="G24" s="49"/>
+    </row>
+    <row r="25" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="24"/>
+      <c r="B25" s="23">
+        <v>3</v>
+      </c>
+      <c r="C25" s="80" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="82"/>
+      <c r="G25" s="71" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="141"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="49"/>
+    </row>
+    <row r="27" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="24"/>
+      <c r="B27" s="25">
+        <v>6</v>
+      </c>
+      <c r="C27" s="110" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="71" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="30"/>
+      <c r="B28" s="27">
+        <v>7</v>
+      </c>
+      <c r="C28" s="190" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="191"/>
+      <c r="E28" s="191"/>
+      <c r="F28" s="192"/>
+      <c r="G28" s="66" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="29">
+        <v>1</v>
+      </c>
+      <c r="C29" s="113"/>
+      <c r="D29" s="114"/>
+      <c r="E29" s="114"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="70"/>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="31"/>
+      <c r="B30" s="25">
+        <v>2</v>
+      </c>
+      <c r="C30" s="92" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="94"/>
+      <c r="G30" s="66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="32"/>
+      <c r="B31" s="33">
+        <v>3</v>
+      </c>
+      <c r="C31" s="166" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="167"/>
+      <c r="E31" s="167"/>
+      <c r="F31" s="168"/>
+      <c r="G31" s="66" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="34"/>
+      <c r="B32" s="27">
+        <v>4</v>
+      </c>
+      <c r="C32" s="122" t="s">
+        <v>29</v>
+      </c>
+      <c r="D32" s="123"/>
+      <c r="E32" s="123"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="67" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="29">
+        <v>1</v>
+      </c>
+      <c r="C33" s="172" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="173"/>
+      <c r="E33" s="173"/>
+      <c r="F33" s="174"/>
+      <c r="G33" s="48"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A34" s="36"/>
+      <c r="B34" s="25">
+        <v>2</v>
+      </c>
+      <c r="C34" s="175"/>
+      <c r="D34" s="176"/>
+      <c r="E34" s="176"/>
+      <c r="F34" s="177"/>
+      <c r="G34" s="59"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A35" s="36"/>
+      <c r="B35" s="25">
+        <v>3</v>
+      </c>
+      <c r="C35" s="140"/>
+      <c r="D35" s="141"/>
+      <c r="E35" s="141"/>
+      <c r="F35" s="142"/>
+      <c r="G35" s="59"/>
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="37"/>
+      <c r="B36" s="27">
+        <v>4</v>
+      </c>
+      <c r="C36" s="169"/>
+      <c r="D36" s="170"/>
+      <c r="E36" s="170"/>
+      <c r="F36" s="171"/>
+      <c r="G36" s="58"/>
+    </row>
+    <row r="37" spans="1:7" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="38"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="131"/>
+      <c r="D37" s="132"/>
+      <c r="E37" s="132"/>
+      <c r="F37" s="133"/>
+      <c r="G37" s="40"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="51"/>
+      <c r="B38" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="178" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="179"/>
+      <c r="E38" s="179"/>
+      <c r="F38" s="180"/>
+      <c r="G38" s="69" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="53"/>
+      <c r="B39" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="110" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" s="111"/>
+      <c r="E39" s="111"/>
+      <c r="F39" s="112"/>
+      <c r="G39" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="167"/>
-      <c r="E16" s="167"/>
-      <c r="F16" s="168"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
-        <v>3</v>
-      </c>
-      <c r="C17" s="124"/>
-      <c r="D17" s="125"/>
-      <c r="E17" s="125"/>
-      <c r="F17" s="126"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24">
-        <v>4</v>
-      </c>
-      <c r="C18" s="118"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="120"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="52"/>
-      <c r="B19" s="32">
-        <v>5</v>
-      </c>
-      <c r="C19" s="124" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="125"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="126"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="28">
-        <v>1</v>
-      </c>
-      <c r="C20" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="81"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
-        <v>2</v>
-      </c>
-      <c r="C21" s="133"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="134"/>
-      <c r="F21" s="135"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24">
-        <v>3</v>
-      </c>
-      <c r="C22" s="136"/>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="138"/>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="29"/>
-      <c r="B23" s="26">
-        <v>4</v>
-      </c>
-      <c r="C23" s="139"/>
-      <c r="D23" s="140"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="141"/>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="22">
-        <v>2</v>
-      </c>
-      <c r="C24" s="88"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="90"/>
-    </row>
-    <row r="25" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="22">
-        <v>3</v>
-      </c>
-      <c r="C25" s="85" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="87"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="89"/>
-      <c r="F26" s="90"/>
-    </row>
-    <row r="27" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="23"/>
-      <c r="B27" s="24">
-        <v>6</v>
-      </c>
-      <c r="C27" s="124" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" s="125"/>
-      <c r="E27" s="125"/>
-      <c r="F27" s="126"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="29"/>
-      <c r="B28" s="26">
-        <v>7</v>
-      </c>
-      <c r="C28" s="142" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="143"/>
-      <c r="E28" s="143"/>
-      <c r="F28" s="144"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="28">
-        <v>1</v>
-      </c>
-      <c r="C29" s="127"/>
-      <c r="D29" s="128"/>
-      <c r="E29" s="128"/>
-      <c r="F29" s="129"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="30"/>
-      <c r="B30" s="24">
-        <v>2</v>
-      </c>
-      <c r="C30" s="57" t="s">
-        <v>51</v>
-      </c>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="59"/>
-    </row>
-    <row r="31" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="31"/>
-      <c r="B31" s="32">
-        <v>3</v>
-      </c>
-      <c r="C31" s="151" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
-      <c r="F31" s="153"/>
-    </row>
-    <row r="32" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="33"/>
-      <c r="B32" s="26">
-        <v>4</v>
-      </c>
-      <c r="C32" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="68"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="69"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="28">
-        <v>1</v>
-      </c>
-      <c r="C33" s="157" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="158"/>
-      <c r="E33" s="158"/>
-      <c r="F33" s="159"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A34" s="35"/>
-      <c r="B34" s="24">
-        <v>2</v>
-      </c>
-      <c r="C34" s="160"/>
-      <c r="D34" s="161"/>
-      <c r="E34" s="161"/>
-      <c r="F34" s="162"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="35"/>
-      <c r="B35" s="24">
-        <v>3</v>
-      </c>
-      <c r="C35" s="88"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="90"/>
-    </row>
-    <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="36"/>
-      <c r="B36" s="26">
-        <v>4</v>
-      </c>
-      <c r="C36" s="154"/>
-      <c r="D36" s="155"/>
-      <c r="E36" s="155"/>
-      <c r="F36" s="156"/>
-    </row>
-    <row r="37" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="78"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="46"/>
-      <c r="B38" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="163" t="s">
-        <v>41</v>
-      </c>
-      <c r="D38" s="164"/>
-      <c r="E38" s="164"/>
-      <c r="F38" s="165"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A39" s="48"/>
-      <c r="B39" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="124" t="s">
-        <v>42</v>
-      </c>
-      <c r="D39" s="125"/>
-      <c r="E39" s="125"/>
-      <c r="F39" s="126"/>
-    </row>
-    <row r="40" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="50"/>
-      <c r="B40" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="C40" s="148" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="149"/>
-      <c r="E40" s="149"/>
-      <c r="F40" s="150"/>
-    </row>
-    <row r="41" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="55"/>
+      <c r="B40" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="163" t="s">
+        <v>53</v>
+      </c>
+      <c r="D40" s="164"/>
+      <c r="E40" s="164"/>
+      <c r="F40" s="165"/>
+      <c r="G40" s="63" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B41" s="2" t="s">
         <v>13</v>
       </c>
@@ -2949,16 +3272,34 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="C13:F13"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C31:F31"/>
@@ -2975,24 +3316,6 @@
     <mergeCell ref="C38:F38"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5">
@@ -3023,7 +3346,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3032,12 +3355,13 @@
     <col min="4" max="4" width="19" style="2" customWidth="1"/>
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" style="2" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="2"/>
-    <col min="10" max="10" width="7.85546875" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="10" width="9.140625" style="2"/>
+    <col min="11" max="11" width="7.85546875" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3045,15 +3369,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3061,39 +3385,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="43" t="s">
-        <v>16</v>
+      <c r="C6" s="45" t="s">
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3103,35 +3427,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="152" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="152"/>
+      <c r="E7" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="47" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="63" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="C8" s="159" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="159"/>
+      <c r="E8" s="159"/>
+      <c r="F8" s="159"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>0</v>
@@ -3142,328 +3466,391 @@
       <c r="D9" s="18"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="22">
+      <c r="G9" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="23">
         <v>1</v>
       </c>
-      <c r="C10" s="64"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="66"/>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24">
+      <c r="C10" s="160"/>
+      <c r="D10" s="161"/>
+      <c r="E10" s="161"/>
+      <c r="F10" s="162"/>
+      <c r="G10" s="74"/>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="201" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" s="202"/>
-      <c r="E11" s="202"/>
-      <c r="F11" s="203"/>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24">
+      <c r="C11" s="206" t="s">
+        <v>112</v>
+      </c>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
+      <c r="F11" s="208"/>
+      <c r="G11" s="76" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25">
         <v>3</v>
       </c>
-      <c r="C12" s="201" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="202"/>
-      <c r="E12" s="202"/>
-      <c r="F12" s="203"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C12" s="206" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="207"/>
+      <c r="E12" s="207"/>
+      <c r="F12" s="208"/>
+      <c r="G12" s="76" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
         <v>5</v>
       </c>
-      <c r="C13" s="204"/>
-      <c r="D13" s="205"/>
-      <c r="E13" s="205"/>
-      <c r="F13" s="206"/>
-    </row>
-    <row r="14" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="28">
+      <c r="C13" s="196"/>
+      <c r="D13" s="197"/>
+      <c r="E13" s="197"/>
+      <c r="F13" s="198"/>
+      <c r="G13" s="79"/>
+    </row>
+    <row r="14" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="29">
         <v>1</v>
       </c>
-      <c r="C14" s="210" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="211"/>
-      <c r="E14" s="212"/>
-      <c r="F14" s="213"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24">
+      <c r="C14" s="202" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="203"/>
+      <c r="E14" s="204"/>
+      <c r="F14" s="205"/>
+      <c r="G14" s="77" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25">
         <v>2</v>
       </c>
-      <c r="C15" s="207" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="208"/>
-      <c r="E15" s="208"/>
-      <c r="F15" s="209"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24">
+      <c r="C15" s="199" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="200"/>
+      <c r="E15" s="200"/>
+      <c r="F15" s="201"/>
+      <c r="G15" s="66" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25">
         <v>3</v>
       </c>
-      <c r="C16" s="151" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="152"/>
-      <c r="E16" s="152"/>
-      <c r="F16" s="153"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="23"/>
-      <c r="B17" s="24">
+      <c r="C16" s="166" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="167"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="71" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25">
         <v>4</v>
       </c>
-      <c r="C17" s="181" t="s">
-        <v>44</v>
-      </c>
-      <c r="D17" s="182"/>
-      <c r="E17" s="182"/>
-      <c r="F17" s="183"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="52"/>
-      <c r="B18" s="32">
+      <c r="C17" s="212" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="213"/>
+      <c r="E17" s="213"/>
+      <c r="F17" s="214"/>
+      <c r="G17" s="66" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="57"/>
+      <c r="B18" s="33">
         <v>5</v>
       </c>
-      <c r="C18" s="184"/>
-      <c r="D18" s="185"/>
-      <c r="E18" s="185"/>
-      <c r="F18" s="186"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="28">
+      <c r="C18" s="215"/>
+      <c r="D18" s="216"/>
+      <c r="E18" s="216"/>
+      <c r="F18" s="217"/>
+      <c r="G18" s="59"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="29">
         <v>2</v>
       </c>
-      <c r="C19" s="187"/>
-      <c r="D19" s="188"/>
-      <c r="E19" s="188"/>
-      <c r="F19" s="189"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24">
+      <c r="C19" s="218"/>
+      <c r="D19" s="219"/>
+      <c r="E19" s="219"/>
+      <c r="F19" s="220"/>
+      <c r="G19" s="62"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25">
         <v>3</v>
       </c>
-      <c r="C20" s="190" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="191"/>
-      <c r="E20" s="191"/>
-      <c r="F20" s="192"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24">
+      <c r="C20" s="221" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="222"/>
+      <c r="E20" s="222"/>
+      <c r="F20" s="223"/>
+      <c r="G20" s="66" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25">
         <v>4</v>
       </c>
-      <c r="C21" s="190" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="191"/>
-      <c r="E21" s="191"/>
-      <c r="F21" s="192"/>
-    </row>
-    <row r="22" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="26">
+      <c r="C21" s="221" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="222"/>
+      <c r="E21" s="222"/>
+      <c r="F21" s="223"/>
+      <c r="G21" s="66" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="27">
         <v>5</v>
       </c>
-      <c r="C22" s="196"/>
-      <c r="D22" s="197"/>
-      <c r="E22" s="176" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="177"/>
-    </row>
-    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="22">
+      <c r="C22" s="227"/>
+      <c r="D22" s="228"/>
+      <c r="E22" s="229" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" s="230"/>
+      <c r="G22" s="78" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="23">
         <v>2</v>
       </c>
-      <c r="C23" s="198"/>
-      <c r="D23" s="199"/>
-      <c r="E23" s="199"/>
-      <c r="F23" s="200"/>
-    </row>
-    <row r="24" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="22">
+      <c r="C23" s="231"/>
+      <c r="D23" s="232"/>
+      <c r="E23" s="232"/>
+      <c r="F23" s="233"/>
+      <c r="G23" s="71"/>
+    </row>
+    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24"/>
+      <c r="B24" s="23">
         <v>3</v>
       </c>
-      <c r="C24" s="190" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="191"/>
-      <c r="E24" s="191"/>
-      <c r="F24" s="192"/>
-    </row>
-    <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24">
+      <c r="C24" s="221" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="222"/>
+      <c r="E24" s="222"/>
+      <c r="F24" s="223"/>
+      <c r="G24" s="66" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25">
         <v>4</v>
       </c>
-      <c r="C25" s="190" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="191"/>
-      <c r="E25" s="191"/>
-      <c r="F25" s="192"/>
-    </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="26">
+      <c r="C25" s="221" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="222"/>
+      <c r="E25" s="222"/>
+      <c r="F25" s="223"/>
+      <c r="G25" s="66" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="30"/>
+      <c r="B26" s="27">
         <v>5</v>
       </c>
-      <c r="C26" s="193" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="194"/>
-      <c r="E26" s="194"/>
-      <c r="F26" s="195"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="28">
+      <c r="C26" s="224" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="225"/>
+      <c r="E26" s="225"/>
+      <c r="F26" s="226"/>
+      <c r="G26" s="66" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="29">
         <v>1</v>
       </c>
-      <c r="C27" s="178"/>
-      <c r="D27" s="179"/>
-      <c r="E27" s="179"/>
-      <c r="F27" s="180"/>
-    </row>
-    <row r="28" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="24">
+      <c r="C27" s="209"/>
+      <c r="D27" s="210"/>
+      <c r="E27" s="210"/>
+      <c r="F27" s="211"/>
+      <c r="G27" s="48"/>
+    </row>
+    <row r="28" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="25">
         <v>2</v>
       </c>
-      <c r="C28" s="172"/>
-      <c r="D28" s="173"/>
-      <c r="E28" s="173"/>
-      <c r="F28" s="174"/>
-    </row>
-    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="31"/>
-      <c r="B29" s="32">
+      <c r="C28" s="237"/>
+      <c r="D28" s="238"/>
+      <c r="E28" s="238"/>
+      <c r="F28" s="239"/>
+      <c r="G28" s="59"/>
+    </row>
+    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="32"/>
+      <c r="B29" s="33">
         <v>3</v>
       </c>
-      <c r="C29" s="133"/>
-      <c r="D29" s="134"/>
-      <c r="E29" s="134"/>
-      <c r="F29" s="135"/>
-    </row>
-    <row r="30" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="33"/>
-      <c r="B30" s="26">
+      <c r="C29" s="119"/>
+      <c r="D29" s="120"/>
+      <c r="E29" s="120"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="59"/>
+    </row>
+    <row r="30" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="34"/>
+      <c r="B30" s="27">
         <v>4</v>
       </c>
-      <c r="C30" s="175" t="s">
-        <v>71</v>
-      </c>
-      <c r="D30" s="176"/>
-      <c r="E30" s="176"/>
-      <c r="F30" s="177"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A31" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="28">
+      <c r="C30" s="240" t="s">
+        <v>101</v>
+      </c>
+      <c r="D30" s="229"/>
+      <c r="E30" s="229"/>
+      <c r="F30" s="230"/>
+      <c r="G30" s="68" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A31" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="29">
         <v>1</v>
       </c>
-      <c r="C31" s="73"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="35"/>
-      <c r="B32" s="24">
+      <c r="C31" s="128"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="129"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="48"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="36"/>
+      <c r="B32" s="25">
         <v>2</v>
       </c>
-      <c r="C32" s="82" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="84"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="35"/>
-      <c r="B33" s="24">
+      <c r="C32" s="137" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="138"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="139"/>
+      <c r="G32" s="66" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="36"/>
+      <c r="B33" s="25">
         <v>3</v>
       </c>
-      <c r="C33" s="82" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="84"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="36"/>
-      <c r="B34" s="26">
+      <c r="C33" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" s="138"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="139"/>
+      <c r="G33" s="71" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="37"/>
+      <c r="B34" s="27">
         <v>4</v>
       </c>
-      <c r="C34" s="154"/>
-      <c r="D34" s="155"/>
-      <c r="E34" s="155"/>
-      <c r="F34" s="156"/>
-    </row>
-    <row r="35" spans="1:6" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="78"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="46"/>
-      <c r="B36" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="C36" s="163" t="s">
-        <v>63</v>
-      </c>
-      <c r="D36" s="164"/>
-      <c r="E36" s="164"/>
-      <c r="F36" s="165"/>
-    </row>
-    <row r="37" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="50"/>
-      <c r="B37" s="51"/>
-      <c r="C37" s="169"/>
-      <c r="D37" s="170"/>
-      <c r="E37" s="170"/>
-      <c r="F37" s="171"/>
-    </row>
-    <row r="38" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C34" s="169"/>
+      <c r="D34" s="170"/>
+      <c r="E34" s="170"/>
+      <c r="F34" s="171"/>
+      <c r="G34" s="58"/>
+    </row>
+    <row r="35" spans="1:7" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="38"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="131"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="132"/>
+      <c r="F35" s="133"/>
+      <c r="G35" s="40"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="51"/>
+      <c r="B36" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="178" t="s">
+        <v>87</v>
+      </c>
+      <c r="D36" s="179"/>
+      <c r="E36" s="179"/>
+      <c r="F36" s="180"/>
+      <c r="G36" s="69" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="55"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="234"/>
+      <c r="D37" s="235"/>
+      <c r="E37" s="235"/>
+      <c r="F37" s="236"/>
+      <c r="G37" s="50"/>
+    </row>
+    <row r="38" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
         <v>13</v>
       </c>
@@ -3471,26 +3858,26 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
@@ -3503,16 +3890,16 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5">
